--- a/pharmapromo-import.xlsx
+++ b/pharmapromo-import.xlsx
@@ -76,25 +76,25 @@
     <t>Prix promo</t>
   </si>
   <si>
-    <t>COMPLÉMENT ALIMENTAIRE</t>
-  </si>
-  <si>
-    <t>Chondro-Aid Fort ARKOPHARMA</t>
-  </si>
-  <si>
-    <t>Lot de 3 x 60 gélules</t>
+    <t>SOIN VISAGE</t>
+  </si>
+  <si>
+    <t>Eau Thermale AVÈNE Hydrance légère</t>
+  </si>
+  <si>
+    <t>Tube 40 ml</t>
   </si>
   <si>
     <t>A4</t>
   </si>
   <si>
-    <t>SOIN VISAGE</t>
-  </si>
-  <si>
-    <t>Crème hydratante AVÈNE Hydrance</t>
-  </si>
-  <si>
-    <t>Tube 40 ml</t>
+    <t>CAPILLAIRE</t>
+  </si>
+  <si>
+    <t>Shampooing KLORANE à l’ortie blanche</t>
+  </si>
+  <si>
+    <t>Flacon 400 ml</t>
   </si>
   <si>
     <t>Vitrine</t>
@@ -103,286 +103,280 @@
     <t>HYGIÈNE BUCCO-DENTAIRE</t>
   </si>
   <si>
-    <t>Bain de bouche ELUDRIL</t>
+    <t>Dentifrice ELMEX Anti-caries</t>
+  </si>
+  <si>
+    <t>Tube 75 ml</t>
+  </si>
+  <si>
+    <t>Rayon</t>
+  </si>
+  <si>
+    <t>PHYTOTHÉRAPIE</t>
+  </si>
+  <si>
+    <t>Aboca Sollievo transit</t>
+  </si>
+  <si>
+    <t>90 comprimés</t>
+  </si>
+  <si>
+    <t>Petite</t>
+  </si>
+  <si>
+    <t>DRAINAGE</t>
+  </si>
+  <si>
+    <t>HERBESAN Draineur bio agrumes</t>
   </si>
   <si>
     <t>Flacon 500 ml</t>
   </si>
   <si>
-    <t>Rayon</t>
-  </si>
-  <si>
-    <t>CAPILLAIRE</t>
-  </si>
-  <si>
-    <t>Shampooing KLORANE Ortie</t>
-  </si>
-  <si>
-    <t>Flacon 400 ml</t>
-  </si>
-  <si>
-    <t>Petite</t>
+    <t>Réglette</t>
+  </si>
+  <si>
+    <t>LUXÉOL Cheveux croissance et vitalité</t>
+  </si>
+  <si>
+    <t>60 gélules</t>
+  </si>
+  <si>
+    <t>ROGER &amp; GALLET Bois d’Orange gel douche</t>
+  </si>
+  <si>
+    <t>Flacon 200 ml</t>
+  </si>
+  <si>
+    <t>DIGESTION</t>
+  </si>
+  <si>
+    <t>PROBIOLOG Fort équilibre intestinal</t>
+  </si>
+  <si>
+    <t>30 gélules</t>
+  </si>
+  <si>
+    <t>SOMMEIL</t>
+  </si>
+  <si>
+    <t>SANTAROME Bio nuit tranquille</t>
+  </si>
+  <si>
+    <t>20 ampoules</t>
   </si>
   <si>
     <t>MINCEUR</t>
   </si>
   <si>
-    <t>Draineur ARKOFLUIDE Bio</t>
-  </si>
-  <si>
-    <t>Réglette</t>
-  </si>
-  <si>
-    <t>VITAMINES</t>
-  </si>
-  <si>
-    <t>Magnésium Marin BIANE</t>
+    <t>STC NUTRITION Draineur 5 actions</t>
+  </si>
+  <si>
+    <t>CIRCULATION</t>
+  </si>
+  <si>
+    <t>LES 3 CHÊNES Jambes légères confort</t>
   </si>
   <si>
     <t>60 comprimés</t>
   </si>
   <si>
+    <t>PREMIERS SOINS</t>
+  </si>
+  <si>
+    <t>Pansements ELASTOPLAST résistants</t>
+  </si>
+  <si>
+    <t>Boîte de 20</t>
+  </si>
+  <si>
+    <t>CORPS</t>
+  </si>
+  <si>
+    <t>Huile de soin BI-OIL F/200ML</t>
+  </si>
+  <si>
+    <t>SOLAIRE</t>
+  </si>
+  <si>
+    <t>DAYLONG Sensitive lait solaire SPF50+</t>
+  </si>
+  <si>
+    <t>Bon</t>
+  </si>
+  <si>
+    <t>Bain de bouche MERIDOL protection gencives</t>
+  </si>
+  <si>
+    <t>31/12/2026</t>
+  </si>
+  <si>
+    <t>BÉBÉ</t>
+  </si>
+  <si>
+    <t>BIOLANE Lingettes à l’eau</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
+  </si>
+  <si>
+    <t>VÉTÉRINAIRE</t>
+  </si>
+  <si>
+    <t>CLÉMENT THÉKAN antiparasitaire chien</t>
+  </si>
+  <si>
+    <t>15/11/2026</t>
+  </si>
+  <si>
+    <t>ANTI-POUX</t>
+  </si>
+  <si>
+    <t>POUXIT Lotion traitante</t>
+  </si>
+  <si>
+    <t>INCONTINENCE</t>
+  </si>
+  <si>
+    <t>Protections TENA Lady Discreet</t>
+  </si>
+  <si>
+    <t>31/10/2026</t>
+  </si>
+  <si>
+    <t>AUTODIAGNOSTIC</t>
+  </si>
+  <si>
+    <t>CLEARBLUE test de grossesse digital</t>
+  </si>
+  <si>
+    <t>Lot</t>
+  </si>
+  <si>
+    <t>HYGIÈNE INTIME</t>
+  </si>
+  <si>
+    <t>Gel lavant SAFORELLE soin doux</t>
+  </si>
+  <si>
+    <t>Lot de 2 flacons</t>
+  </si>
+  <si>
+    <t>DAYLONG Spray solaire SPF30</t>
+  </si>
+  <si>
+    <t>Lot de 2 sprays</t>
+  </si>
+  <si>
+    <t>NEUTRADERM Gel douche surgras</t>
+  </si>
+  <si>
+    <t>IMMUNITÉ</t>
+  </si>
+  <si>
+    <t>SANTÉ VERTE Vitamine C acérola</t>
+  </si>
+  <si>
+    <t>Lot de 2 tubes</t>
+  </si>
+  <si>
+    <t>HYDRALIN Quotidien gel lavant</t>
+  </si>
+  <si>
+    <t>Shampooing DUCRAY Kertyol état pelliculaire</t>
+  </si>
+  <si>
+    <t>SOINS DES LÈVRES</t>
+  </si>
+  <si>
+    <t>LAINO Stick lèvres karité</t>
+  </si>
+  <si>
+    <t>Lot de 2 sticks</t>
+  </si>
+  <si>
+    <t>MICRONUTRITION</t>
+  </si>
+  <si>
+    <t>THALAMAG Magnésium marin fatigue</t>
+  </si>
+  <si>
+    <t>30 comprimés</t>
+  </si>
+  <si>
+    <t>Multi</t>
+  </si>
+  <si>
+    <t>PROTECTION AUDITIVE</t>
+  </si>
+  <si>
+    <t>QUIES Boules Quies cire naturelle</t>
+  </si>
+  <si>
+    <t>TEPE Brossettes interdentaires</t>
+  </si>
+  <si>
+    <t>ANTI-MOUSTIQUES</t>
+  </si>
+  <si>
+    <t>PARAKITO Recharges bracelet répulsif</t>
+  </si>
+  <si>
+    <t>SOIN DES ONGLES</t>
+  </si>
+  <si>
+    <t>MAVALA Vernis à ongles couleur</t>
+  </si>
+  <si>
+    <t>PAMPERS Baby-Dry taille 4 mégapack</t>
+  </si>
+  <si>
+    <t>IPHYM Tisane digestion bio</t>
+  </si>
+  <si>
+    <t>2ᵉ produit</t>
+  </si>
+  <si>
     <t>DERMO-COSMÉTIQUE</t>
   </si>
   <si>
-    <t>Sérum La Roche-Posay Hyalu B5</t>
-  </si>
-  <si>
-    <t>Flacon 30 ml</t>
-  </si>
-  <si>
-    <t>DIGESTION</t>
-  </si>
-  <si>
-    <t>Probiotiques LACTIBIANE Référence</t>
-  </si>
-  <si>
-    <t>30 gélules</t>
-  </si>
-  <si>
-    <t>SOMMEIL</t>
-  </si>
-  <si>
-    <t>Mélatonine 1,9 mg NUTRISANTÉ</t>
-  </si>
-  <si>
-    <t>30 comprimés</t>
-  </si>
-  <si>
-    <t>ARTICULATIONS</t>
-  </si>
-  <si>
-    <t>Flexofytol PHYSIOMANCE</t>
-  </si>
-  <si>
-    <t>60 capsules</t>
-  </si>
-  <si>
-    <t>CIRCULATION</t>
-  </si>
-  <si>
-    <t>Veinotonique CIRKAN</t>
-  </si>
-  <si>
-    <t>PREMIERS SOINS</t>
-  </si>
-  <si>
-    <t>Pansements URGO Waterproof</t>
-  </si>
-  <si>
-    <t>Boîte de 20</t>
-  </si>
-  <si>
-    <t>CORPS</t>
-  </si>
-  <si>
-    <t>Lait hydratant CERAVE F/473ML</t>
-  </si>
-  <si>
-    <t>SOLAIRE</t>
-  </si>
-  <si>
-    <t>Lait solaire ANTHELIOS SPF50+</t>
+    <t>ROC Retinol Correxion crème nuit</t>
+  </si>
+  <si>
+    <t>Pot 30 ml</t>
+  </si>
+  <si>
+    <t>Bain de bouche CB12 haleine fraîche</t>
   </si>
   <si>
     <t>Flacon 250 ml</t>
   </si>
   <si>
-    <t>Bon</t>
-  </si>
-  <si>
-    <t>HYGIÈNE</t>
-  </si>
-  <si>
-    <t>Dentifrice SENSODYNE Répare &amp; Protège</t>
-  </si>
-  <si>
-    <t>31/12/2026</t>
-  </si>
-  <si>
-    <t>BÉBÉ</t>
-  </si>
-  <si>
-    <t>Lingettes MUSTELA</t>
-  </si>
-  <si>
-    <t>30/09/2026</t>
-  </si>
-  <si>
-    <t>VÉTÉRINAIRE</t>
-  </si>
-  <si>
-    <t>Antiparasitaire FRONTLINE Combo</t>
-  </si>
-  <si>
-    <t>15/11/2026</t>
-  </si>
-  <si>
-    <t>SEVRAGE TABAGIQUE</t>
-  </si>
-  <si>
-    <t>Patchs NICORETTE 25 mg</t>
-  </si>
-  <si>
-    <t>INCONTINENCE</t>
-  </si>
-  <si>
-    <t>Protections TENA Lady</t>
-  </si>
-  <si>
-    <t>31/10/2026</t>
-  </si>
-  <si>
-    <t>ORTHOPÉDIE</t>
-  </si>
-  <si>
-    <t>Ceinture lombaire THUASNE</t>
-  </si>
-  <si>
-    <t>Lot</t>
-  </si>
-  <si>
-    <t>Magnésium B6 SANOFI</t>
-  </si>
-  <si>
-    <t>Lot de 2 boîtes</t>
-  </si>
-  <si>
-    <t>Spray solaire BIODERMA SPF50+</t>
-  </si>
-  <si>
-    <t>Lot de 2 sprays</t>
-  </si>
-  <si>
-    <t>Gel douche SANEX Zéro%</t>
-  </si>
-  <si>
-    <t>Lot de 2 flacons</t>
-  </si>
-  <si>
-    <t>IMMUNITÉ</t>
-  </si>
-  <si>
-    <t>Vitamine C AZINC</t>
-  </si>
-  <si>
-    <t>Lot de 2 tubes</t>
-  </si>
-  <si>
-    <t>HYGIÈNE INTIME</t>
-  </si>
-  <si>
-    <t>Gel lavant SAFORELLE</t>
-  </si>
-  <si>
-    <t>Shampooing DUCRAY Kertyol</t>
-  </si>
-  <si>
-    <t>SOINS DES LÈVRES</t>
-  </si>
-  <si>
-    <t>Stick lèvres LABELLO</t>
-  </si>
-  <si>
-    <t>Lot de 2 sticks</t>
-  </si>
-  <si>
-    <t>NUTRITION SPORTIVE</t>
-  </si>
-  <si>
-    <t>Shaker protéiné EAFIT</t>
-  </si>
-  <si>
-    <t>1 acheté + 1 offert</t>
-  </si>
-  <si>
-    <t>Multi</t>
-  </si>
-  <si>
-    <t>Spray solaire GARNIER SPF50</t>
-  </si>
-  <si>
-    <t>Savon de Marseille LE PETIT MARSEILLAIS</t>
-  </si>
-  <si>
-    <t>Barre protéinée EAFIT</t>
-  </si>
-  <si>
-    <t>YEUX</t>
-  </si>
-  <si>
-    <t>Sérum physiologique dosettes</t>
-  </si>
-  <si>
-    <t>Couches PAMPERS Baby-Dry T4</t>
-  </si>
-  <si>
-    <t>DIÉTÉTIQUE</t>
-  </si>
-  <si>
-    <t>Infusion detox BIO</t>
-  </si>
-  <si>
-    <t>2ᵉ produit</t>
-  </si>
-  <si>
-    <t>Crème mains NEUTROGENA</t>
-  </si>
-  <si>
-    <t>Tube 75 ml</t>
-  </si>
-  <si>
-    <t>Bain de bouche LISTERINE</t>
-  </si>
-  <si>
-    <t>CONTOUR DES YEUX</t>
-  </si>
-  <si>
-    <t>Soin anti-âge CAUDALIE Resvératrol</t>
-  </si>
-  <si>
-    <t>Pot 15 ml</t>
+    <t>ELANCYL Slim Design fermeté</t>
+  </si>
+  <si>
+    <t>Tube 200 ml</t>
   </si>
   <si>
     <t>PIEDS</t>
   </si>
   <si>
-    <t>Crème anti-callosités AKILEÏNE</t>
-  </si>
-  <si>
-    <t>MAQUILLAGE</t>
-  </si>
-  <si>
-    <t>Fond de teint AVÈNE Couvrance</t>
+    <t>Crème anti-callosités AKILÉÏNE</t>
+  </si>
+  <si>
+    <t>JOWAÉ Crème lissante hydratante</t>
+  </si>
+  <si>
+    <t>Pot 40 ml</t>
   </si>
   <si>
     <t>HOMME</t>
   </si>
   <si>
-    <t>Gel de rasage GILLETTE Series</t>
-  </si>
-  <si>
-    <t>Tube 200 ml</t>
+    <t>EAU PRÉCIEUSE Lotion soin visage</t>
+  </si>
+  <si>
+    <t>Flacon 375 ml</t>
   </si>
 </sst>
 </file>
@@ -534,10 +528,10 @@
         <v>21</v>
       </c>
       <c r="D2" s="2">
-        <v>31.9</v>
+        <v>19.9</v>
       </c>
       <c r="E2" s="2">
-        <v>26.9</v>
+        <v>14.9</v>
       </c>
       <c r="R2" t="s">
         <v>22</v>
@@ -557,10 +551,10 @@
         <v>25</v>
       </c>
       <c r="D3" s="2">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="E3" s="2">
-        <v>14.9</v>
+        <v>6.9</v>
       </c>
       <c r="R3" t="s">
         <v>26</v>
@@ -580,10 +574,10 @@
         <v>29</v>
       </c>
       <c r="D4" s="2">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="E4" s="2">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
@@ -603,10 +597,10 @@
         <v>33</v>
       </c>
       <c r="D5" s="2">
-        <v>9.9</v>
+        <v>15.5</v>
       </c>
       <c r="E5" s="2">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="R5" t="s">
         <v>34</v>
@@ -626,16 +620,16 @@
         <v>37</v>
       </c>
       <c r="D6" s="2">
-        <v>15.5</v>
+        <v>18.9</v>
       </c>
       <c r="E6" s="2">
-        <v>11.9</v>
+        <v>13.9</v>
       </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="S6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -643,16 +637,16 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="2">
-        <v>13.2</v>
+        <v>24.9</v>
       </c>
       <c r="E7" s="2">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="R7" t="s">
         <v>41</v>
@@ -666,19 +660,19 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="R8" t="s">
         <v>43</v>
-      </c>
-      <c r="D8" s="2">
-        <v>39.9</v>
-      </c>
-      <c r="E8" s="2">
-        <v>31.9</v>
-      </c>
-      <c r="R8" t="s">
-        <v>44</v>
       </c>
       <c r="S8" t="s">
         <v>23</v>
@@ -689,10 +683,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
         <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
       </c>
       <c r="D9" s="2">
         <v>24.9</v>
@@ -701,7 +695,7 @@
         <v>18.9</v>
       </c>
       <c r="R9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S9" t="s">
         <v>27</v>
@@ -712,19 +706,19 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="R10" t="s">
         <v>49</v>
-      </c>
-      <c r="D10" s="2">
-        <v>12.9</v>
-      </c>
-      <c r="E10" s="2">
-        <v>8.9</v>
-      </c>
-      <c r="R10" t="s">
-        <v>50</v>
       </c>
       <c r="S10" t="s">
         <v>35</v>
@@ -735,19 +729,19 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
         <v>51</v>
       </c>
-      <c r="C11" t="s">
-        <v>52</v>
-      </c>
       <c r="D11" s="2">
-        <v>29.9</v>
+        <v>22.9</v>
       </c>
       <c r="E11" s="2">
-        <v>23.9</v>
+        <v>17.5</v>
       </c>
       <c r="R11" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="S11" t="s">
         <v>31</v>
@@ -758,10 +752,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="2">
         <v>17.9</v>
@@ -770,10 +764,10 @@
         <v>13.5</v>
       </c>
       <c r="R12" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="S12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -781,10 +775,10 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
         <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
       </c>
       <c r="D13" s="2">
         <v>5.9</v>
@@ -793,7 +787,7 @@
         <v>3.9</v>
       </c>
       <c r="R13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S13" t="s">
         <v>35</v>
@@ -804,10 +798,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
         <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>60</v>
       </c>
       <c r="D14" s="2">
         <v>16.9</v>
@@ -824,10 +818,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
         <v>61</v>
-      </c>
-      <c r="C15" t="s">
-        <v>62</v>
       </c>
       <c r="D15" s="2">
         <v>24.5</v>
@@ -836,7 +830,7 @@
         <v>19.9</v>
       </c>
       <c r="R15" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="S15" t="s">
         <v>23</v>
@@ -844,19 +838,19 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F16" s="2">
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="S16" t="s">
         <v>27</v>
@@ -864,19 +858,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F17" s="2">
         <v>1.5</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="S17" t="s">
         <v>31</v>
@@ -884,19 +878,19 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F18" s="2">
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="S18" t="s">
         <v>23</v>
@@ -904,19 +898,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F19" s="2">
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="S19" t="s">
         <v>27</v>
@@ -924,19 +918,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F20" s="2">
         <v>2.5</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="S20" t="s">
         <v>31</v>
@@ -944,19 +938,19 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="2">
+        <v>4</v>
+      </c>
+      <c r="G21" t="s">
         <v>64</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="2">
-        <v>10</v>
-      </c>
-      <c r="G21" t="s">
-        <v>67</v>
       </c>
       <c r="S21" t="s">
         <v>23</v>
@@ -964,16 +958,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D22" s="2">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="H22" s="3">
         <v>2</v>
@@ -982,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="2">
-        <v>19.98</v>
+        <v>13.9</v>
       </c>
       <c r="R22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="S22" t="s">
         <v>23</v>
@@ -993,13 +987,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D23" s="2">
         <v>15.9</v>
@@ -1014,21 +1008,21 @@
         <v>24.9</v>
       </c>
       <c r="R23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="S23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D24" s="2">
         <v>5.9</v>
@@ -1043,7 +1037,7 @@
         <v>9.8</v>
       </c>
       <c r="R24" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="S24" t="s">
         <v>31</v>
@@ -1051,13 +1045,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D25" s="2">
         <v>9.9</v>
@@ -1072,7 +1066,7 @@
         <v>15.9</v>
       </c>
       <c r="R25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S25" t="s">
         <v>35</v>
@@ -1080,16 +1074,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D26" s="2">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="H26" s="3">
         <v>2</v>
@@ -1098,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="2">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="R26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="S26" t="s">
         <v>27</v>
@@ -1109,13 +1103,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D27" s="2">
         <v>13.5</v>
@@ -1130,7 +1124,7 @@
         <v>21.9</v>
       </c>
       <c r="R27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="S27" t="s">
         <v>23</v>
@@ -1138,13 +1132,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D28" s="2">
         <v>3.5</v>
@@ -1159,7 +1153,7 @@
         <v>5.5</v>
       </c>
       <c r="R28" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="S28" t="s">
         <v>35</v>
@@ -1167,13 +1161,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D29" s="2">
         <v>19.9</v>
@@ -1188,39 +1182,39 @@
         <v>19.9</v>
       </c>
       <c r="R29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="S29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K30" s="3">
         <v>1</v>
       </c>
       <c r="L30" s="3">
-        <v>12.9</v>
+        <v>5.9</v>
       </c>
       <c r="M30" s="3">
         <v>2</v>
       </c>
       <c r="N30" s="3">
-        <v>22.9</v>
+        <v>10.9</v>
       </c>
       <c r="O30" s="3">
         <v>3</v>
       </c>
       <c r="P30" s="3">
-        <v>29.9</v>
+        <v>14.9</v>
       </c>
       <c r="S30" t="s">
         <v>35</v>
@@ -1228,31 +1222,31 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K31" s="3">
         <v>1</v>
       </c>
       <c r="L31" s="3">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="M31" s="3">
         <v>3</v>
       </c>
       <c r="N31" s="3">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="O31" s="3">
         <v>5</v>
       </c>
       <c r="P31" s="3">
-        <v>13.5</v>
+        <v>21.9</v>
       </c>
       <c r="S31" t="s">
         <v>31</v>
@@ -1260,63 +1254,63 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
         <v>100</v>
       </c>
-      <c r="B32" t="s">
-        <v>97</v>
-      </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K32" s="3">
         <v>1</v>
       </c>
       <c r="L32" s="3">
-        <v>2.5</v>
+        <v>9.9</v>
       </c>
       <c r="M32" s="3">
+        <v>2</v>
+      </c>
+      <c r="N32" s="3">
+        <v>17.9</v>
+      </c>
+      <c r="O32" s="3">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
-        <v>6</v>
-      </c>
-      <c r="O32" s="3">
-        <v>6</v>
-      </c>
       <c r="P32" s="3">
-        <v>10</v>
+        <v>24.9</v>
       </c>
       <c r="S32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K33" s="3">
         <v>1</v>
       </c>
       <c r="L33" s="3">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="M33" s="3">
         <v>2</v>
       </c>
       <c r="N33" s="3">
-        <v>6.9</v>
+        <v>11.9</v>
       </c>
       <c r="O33" s="3">
         <v>3</v>
       </c>
       <c r="P33" s="3">
-        <v>8.9</v>
+        <v>16.5</v>
       </c>
       <c r="S33" t="s">
         <v>27</v>
@@ -1324,13 +1318,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K34" s="3">
         <v>1</v>
@@ -1356,13 +1350,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K35" s="3">
         <v>1</v>
@@ -1388,22 +1382,22 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D36" s="2">
-        <v>4.95</v>
+        <v>32</v>
       </c>
       <c r="Q36" s="3">
         <v>50</v>
       </c>
       <c r="R36" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S36" t="s">
         <v>23</v>
@@ -1411,22 +1405,22 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B37" t="s">
         <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D37" s="2">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q37" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R37" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="S37" t="s">
         <v>27</v>
@@ -1434,22 +1428,22 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="2">
+        <v>28.9</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>40</v>
+      </c>
+      <c r="R38" t="s">
         <v>113</v>
-      </c>
-      <c r="C38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" s="2">
-        <v>32</v>
-      </c>
-      <c r="Q38" s="3">
-        <v>50</v>
-      </c>
-      <c r="R38" t="s">
-        <v>115</v>
       </c>
       <c r="S38" t="s">
         <v>31</v>
@@ -1457,13 +1451,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D39" s="2">
         <v>8.9</v>
@@ -1472,7 +1466,7 @@
         <v>40</v>
       </c>
       <c r="R39" t="s">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="S39" t="s">
         <v>35</v>
@@ -1480,13 +1474,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D40" s="2">
         <v>18.5</v>
@@ -1495,21 +1489,21 @@
         <v>50</v>
       </c>
       <c r="R40" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="S40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D41" s="2">
         <v>5.4</v>
@@ -1518,7 +1512,7 @@
         <v>30</v>
       </c>
       <c r="R41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="S41" t="s">
         <v>31</v>
